--- a/template.xlsx
+++ b/template.xlsx
@@ -464,20 +464,66 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="11" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" shrinkToFit="1"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" shrinkToFit="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
@@ -486,52 +532,6 @@
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" shrinkToFit="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="1" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" shrinkToFit="1"/>
     </xf>
   </cellXfs>
@@ -590,15 +590,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>1</xdr:col>
-      <xdr:colOff>7814</xdr:colOff>
+      <xdr:colOff>5115</xdr:colOff>
       <xdr:row>23</xdr:row>
-      <xdr:rowOff>28409</xdr:rowOff>
+      <xdr:rowOff>18885</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>845025</xdr:colOff>
+      <xdr:colOff>847725</xdr:colOff>
       <xdr:row>44</xdr:row>
-      <xdr:rowOff>142875</xdr:rowOff>
+      <xdr:rowOff>152400</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -611,8 +611,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="74489" y="3933659"/>
-          <a:ext cx="4952011" cy="3800641"/>
+          <a:off x="71790" y="3924135"/>
+          <a:ext cx="4957410" cy="3819690"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -659,254 +659,6 @@
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>295275</xdr:colOff>
-      <xdr:row>3</xdr:row>
-      <xdr:rowOff>85725</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>657225</xdr:colOff>
-      <xdr:row>16</xdr:row>
-      <xdr:rowOff>0</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="正方形/長方形 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1047750" y="638175"/>
-          <a:ext cx="3105150" cy="2171700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>152399</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>9359</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>276224</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>76034</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="7" name="正方形/長方形 6"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="904874" y="4809959"/>
-          <a:ext cx="1495425" cy="2171700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FF0000"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100"/>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>4</xdr:col>
-      <xdr:colOff>331664</xdr:colOff>
-      <xdr:row>28</xdr:row>
-      <xdr:rowOff>66509</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>6</xdr:col>
-      <xdr:colOff>114300</xdr:colOff>
-      <xdr:row>40</xdr:row>
-      <xdr:rowOff>133184</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="8" name="正方形/長方形 7"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="2455739" y="4867109"/>
-          <a:ext cx="1154236" cy="2171700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor>
-    <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>681180</xdr:colOff>
-      <xdr:row>49</xdr:row>
-      <xdr:rowOff>180810</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>7</xdr:col>
-      <xdr:colOff>19049</xdr:colOff>
-      <xdr:row>62</xdr:row>
-      <xdr:rowOff>66510</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp macro="" textlink="">
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="10" name="正方形/長方形 9"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="1433655" y="8543760"/>
-          <a:ext cx="2766869" cy="2171700"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="28575">
-          <a:solidFill>
-            <a:srgbClr val="FFFF00"/>
-          </a:solidFill>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="lt1"/>
-        </a:fontRef>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr vertOverflow="clip" horzOverflow="clip" rtlCol="0" anchor="t"/>
-        <a:lstStyle/>
-        <a:p>
-          <a:pPr algn="l"/>
-          <a:endParaRPr kumimoji="1" lang="ja-JP" altLang="en-US" sz="1100">
-            <a:solidFill>
-              <a:sysClr val="windowText" lastClr="000000"/>
-            </a:solidFill>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -1045,12 +797,12 @@
       <c r="G1" s="3"/>
       <c r="H1" s="3"/>
       <c r="I1" s="2"/>
-      <c r="J1" s="14" t="s">
+      <c r="J1" s="33" t="s">
         <v>0</v>
       </c>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-      <c r="M1" s="14"/>
+      <c r="K1" s="33"/>
+      <c r="L1" s="33"/>
+      <c r="M1" s="33"/>
     </row>
     <row r="2" spans="2:13" ht="15">
       <c r="B2" s="4"/>
@@ -1061,12 +813,12 @@
       <c r="G2" s="5"/>
       <c r="H2" s="5"/>
       <c r="I2" s="4"/>
-      <c r="J2" s="15" t="s">
+      <c r="J2" s="17" t="s">
         <v>1</v>
       </c>
-      <c r="K2" s="15"/>
-      <c r="L2" s="15"/>
-      <c r="M2" s="15"/>
+      <c r="K2" s="17"/>
+      <c r="L2" s="17"/>
+      <c r="M2" s="17"/>
     </row>
     <row r="3" spans="2:13">
       <c r="B3" s="4"/>
@@ -1077,10 +829,10 @@
       <c r="G3" s="5"/>
       <c r="H3" s="5"/>
       <c r="I3" s="4"/>
-      <c r="J3" s="16"/>
-      <c r="K3" s="16"/>
-      <c r="L3" s="16"/>
-      <c r="M3" s="16"/>
+      <c r="J3" s="34"/>
+      <c r="K3" s="34"/>
+      <c r="L3" s="34"/>
+      <c r="M3" s="34"/>
     </row>
     <row r="4" spans="2:13" ht="15">
       <c r="B4" s="4"/>
@@ -1091,12 +843,12 @@
       <c r="G4" s="5"/>
       <c r="H4" s="5"/>
       <c r="I4" s="4"/>
-      <c r="J4" s="17" t="s">
+      <c r="J4" s="18" t="s">
         <v>2</v>
       </c>
-      <c r="K4" s="17"/>
-      <c r="L4" s="17"/>
-      <c r="M4" s="17"/>
+      <c r="K4" s="18"/>
+      <c r="L4" s="18"/>
+      <c r="M4" s="18"/>
     </row>
     <row r="5" spans="2:13">
       <c r="B5" s="4"/>
@@ -1107,10 +859,10 @@
       <c r="G5" s="5"/>
       <c r="H5" s="5"/>
       <c r="I5" s="4"/>
-      <c r="J5" s="18"/>
-      <c r="K5" s="18"/>
-      <c r="L5" s="18"/>
-      <c r="M5" s="18"/>
+      <c r="J5" s="14"/>
+      <c r="K5" s="14"/>
+      <c r="L5" s="14"/>
+      <c r="M5" s="14"/>
     </row>
     <row r="6" spans="2:13">
       <c r="B6" s="4"/>
@@ -1121,10 +873,10 @@
       <c r="G6" s="5"/>
       <c r="H6" s="5"/>
       <c r="I6" s="4"/>
-      <c r="J6" s="19"/>
-      <c r="K6" s="19"/>
-      <c r="L6" s="19"/>
-      <c r="M6" s="19"/>
+      <c r="J6" s="35"/>
+      <c r="K6" s="35"/>
+      <c r="L6" s="35"/>
+      <c r="M6" s="35"/>
     </row>
     <row r="7" spans="2:13">
       <c r="B7" s="4"/>
@@ -1135,10 +887,10 @@
       <c r="G7" s="5"/>
       <c r="H7" s="5"/>
       <c r="I7" s="4"/>
-      <c r="J7" s="20"/>
-      <c r="K7" s="20"/>
-      <c r="L7" s="20"/>
-      <c r="M7" s="20"/>
+      <c r="J7" s="36"/>
+      <c r="K7" s="36"/>
+      <c r="L7" s="36"/>
+      <c r="M7" s="36"/>
     </row>
     <row r="8" spans="2:13">
       <c r="B8" s="4"/>
@@ -1149,10 +901,10 @@
       <c r="G8" s="5"/>
       <c r="H8" s="5"/>
       <c r="I8" s="4"/>
-      <c r="J8" s="21"/>
-      <c r="K8" s="21"/>
-      <c r="L8" s="21"/>
-      <c r="M8" s="21"/>
+      <c r="J8" s="37"/>
+      <c r="K8" s="37"/>
+      <c r="L8" s="37"/>
+      <c r="M8" s="37"/>
     </row>
     <row r="9" spans="2:13">
       <c r="B9" s="4"/>
@@ -1163,10 +915,10 @@
       <c r="G9" s="5"/>
       <c r="H9" s="5"/>
       <c r="I9" s="4"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="18"/>
-      <c r="L9" s="18"/>
-      <c r="M9" s="18"/>
+      <c r="J9" s="14"/>
+      <c r="K9" s="14"/>
+      <c r="L9" s="14"/>
+      <c r="M9" s="14"/>
     </row>
     <row r="10" spans="2:13" ht="14.25">
       <c r="B10" s="4"/>
@@ -1177,12 +929,12 @@
       <c r="G10" s="5"/>
       <c r="H10" s="5"/>
       <c r="I10" s="4"/>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="K10" s="22"/>
-      <c r="L10" s="22"/>
-      <c r="M10" s="22"/>
+      <c r="K10" s="32"/>
+      <c r="L10" s="32"/>
+      <c r="M10" s="32"/>
     </row>
     <row r="11" spans="2:13">
       <c r="B11" s="4"/>
@@ -1193,10 +945,10 @@
       <c r="G11" s="5"/>
       <c r="H11" s="5"/>
       <c r="I11" s="4"/>
-      <c r="J11" s="23"/>
-      <c r="K11" s="23"/>
-      <c r="L11" s="23"/>
-      <c r="M11" s="23"/>
+      <c r="J11" s="26"/>
+      <c r="K11" s="26"/>
+      <c r="L11" s="26"/>
+      <c r="M11" s="26"/>
     </row>
     <row r="12" spans="2:13">
       <c r="B12" s="4"/>
@@ -1207,10 +959,10 @@
       <c r="G12" s="5"/>
       <c r="H12" s="5"/>
       <c r="I12" s="4"/>
-      <c r="J12" s="24"/>
-      <c r="K12" s="24"/>
-      <c r="L12" s="24"/>
-      <c r="M12" s="24"/>
+      <c r="J12" s="20"/>
+      <c r="K12" s="20"/>
+      <c r="L12" s="20"/>
+      <c r="M12" s="20"/>
     </row>
     <row r="13" spans="2:13">
       <c r="B13" s="4"/>
@@ -1221,10 +973,10 @@
       <c r="G13" s="5"/>
       <c r="H13" s="5"/>
       <c r="I13" s="4"/>
-      <c r="J13" s="18"/>
-      <c r="K13" s="18"/>
-      <c r="L13" s="18"/>
-      <c r="M13" s="18"/>
+      <c r="J13" s="14"/>
+      <c r="K13" s="14"/>
+      <c r="L13" s="14"/>
+      <c r="M13" s="14"/>
     </row>
     <row r="14" spans="2:13">
       <c r="B14" s="4"/>
@@ -1235,10 +987,10 @@
       <c r="G14" s="5"/>
       <c r="H14" s="5"/>
       <c r="I14" s="4"/>
-      <c r="J14" s="18"/>
-      <c r="K14" s="18"/>
-      <c r="L14" s="18"/>
-      <c r="M14" s="18"/>
+      <c r="J14" s="14"/>
+      <c r="K14" s="14"/>
+      <c r="L14" s="14"/>
+      <c r="M14" s="14"/>
     </row>
     <row r="15" spans="2:13">
       <c r="B15" s="4"/>
@@ -1249,10 +1001,10 @@
       <c r="G15" s="5"/>
       <c r="H15" s="5"/>
       <c r="I15" s="4"/>
-      <c r="J15" s="18"/>
-      <c r="K15" s="18"/>
-      <c r="L15" s="18"/>
-      <c r="M15" s="18"/>
+      <c r="J15" s="14"/>
+      <c r="K15" s="14"/>
+      <c r="L15" s="14"/>
+      <c r="M15" s="14"/>
     </row>
     <row r="16" spans="2:13">
       <c r="B16" s="4"/>
@@ -1263,10 +1015,10 @@
       <c r="G16" s="5"/>
       <c r="H16" s="5"/>
       <c r="I16" s="4"/>
-      <c r="J16" s="18"/>
-      <c r="K16" s="18"/>
-      <c r="L16" s="18"/>
-      <c r="M16" s="18"/>
+      <c r="J16" s="14"/>
+      <c r="K16" s="14"/>
+      <c r="L16" s="14"/>
+      <c r="M16" s="14"/>
     </row>
     <row r="17" spans="2:13">
       <c r="B17" s="4"/>
@@ -1277,10 +1029,10 @@
       <c r="G17" s="5"/>
       <c r="H17" s="5"/>
       <c r="I17" s="4"/>
-      <c r="J17" s="18"/>
-      <c r="K17" s="18"/>
-      <c r="L17" s="18"/>
-      <c r="M17" s="18"/>
+      <c r="J17" s="14"/>
+      <c r="K17" s="14"/>
+      <c r="L17" s="14"/>
+      <c r="M17" s="14"/>
     </row>
     <row r="18" spans="2:13">
       <c r="B18" s="4"/>
@@ -1291,10 +1043,10 @@
       <c r="G18" s="5"/>
       <c r="H18" s="5"/>
       <c r="I18" s="4"/>
-      <c r="J18" s="18"/>
-      <c r="K18" s="18"/>
-      <c r="L18" s="18"/>
-      <c r="M18" s="18"/>
+      <c r="J18" s="14"/>
+      <c r="K18" s="14"/>
+      <c r="L18" s="14"/>
+      <c r="M18" s="14"/>
     </row>
     <row r="19" spans="2:13">
       <c r="B19" s="4"/>
@@ -1305,10 +1057,10 @@
       <c r="G19" s="5"/>
       <c r="H19" s="5"/>
       <c r="I19" s="4"/>
-      <c r="J19" s="18"/>
-      <c r="K19" s="18"/>
-      <c r="L19" s="18"/>
-      <c r="M19" s="18"/>
+      <c r="J19" s="14"/>
+      <c r="K19" s="14"/>
+      <c r="L19" s="14"/>
+      <c r="M19" s="14"/>
     </row>
     <row r="20" spans="2:13" ht="15">
       <c r="B20" s="4"/>
@@ -1319,12 +1071,12 @@
       <c r="G20" s="5"/>
       <c r="H20" s="5"/>
       <c r="I20" s="4"/>
-      <c r="J20" s="24" t="s">
+      <c r="J20" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="K20" s="24"/>
-      <c r="L20" s="24"/>
-      <c r="M20" s="24"/>
+      <c r="K20" s="20"/>
+      <c r="L20" s="20"/>
+      <c r="M20" s="20"/>
     </row>
     <row r="21" spans="2:13">
       <c r="B21" s="4"/>
@@ -1335,10 +1087,10 @@
       <c r="G21" s="5"/>
       <c r="H21" s="5"/>
       <c r="I21" s="4"/>
-      <c r="J21" s="25"/>
-      <c r="K21" s="25"/>
-      <c r="L21" s="25"/>
-      <c r="M21" s="25"/>
+      <c r="J21" s="21"/>
+      <c r="K21" s="21"/>
+      <c r="L21" s="21"/>
+      <c r="M21" s="21"/>
     </row>
     <row r="22" spans="2:13" ht="14.25" customHeight="1">
       <c r="B22" s="6"/>
@@ -1376,10 +1128,10 @@
       <c r="G24" s="3"/>
       <c r="H24" s="3"/>
       <c r="I24" s="2"/>
-      <c r="J24" s="26"/>
-      <c r="K24" s="26"/>
-      <c r="L24" s="26"/>
-      <c r="M24" s="26"/>
+      <c r="J24" s="29"/>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29"/>
     </row>
     <row r="25" spans="2:13" ht="15">
       <c r="B25" s="4"/>
@@ -1390,13 +1142,13 @@
       <c r="G25" s="5"/>
       <c r="H25" s="5"/>
       <c r="I25" s="4"/>
-      <c r="J25" s="15" t="str">
+      <c r="J25" s="17" t="str">
         <f>J2</f>
         <v>ミニチュアリレー　#LCM</v>
       </c>
-      <c r="K25" s="15"/>
-      <c r="L25" s="15"/>
-      <c r="M25" s="15"/>
+      <c r="K25" s="17"/>
+      <c r="L25" s="17"/>
+      <c r="M25" s="17"/>
     </row>
     <row r="26" spans="2:13">
       <c r="B26" s="4"/>
@@ -1407,10 +1159,10 @@
       <c r="G26" s="5"/>
       <c r="H26" s="5"/>
       <c r="I26" s="4"/>
-      <c r="J26" s="25"/>
-      <c r="K26" s="25"/>
-      <c r="L26" s="25"/>
-      <c r="M26" s="25"/>
+      <c r="J26" s="21"/>
+      <c r="K26" s="21"/>
+      <c r="L26" s="21"/>
+      <c r="M26" s="21"/>
     </row>
     <row r="27" spans="2:13" ht="15">
       <c r="B27" s="4"/>
@@ -1421,12 +1173,12 @@
       <c r="G27" s="5"/>
       <c r="H27" s="5"/>
       <c r="I27" s="4"/>
-      <c r="J27" s="27" t="s">
+      <c r="J27" s="22" t="s">
         <v>5</v>
       </c>
-      <c r="K27" s="27"/>
-      <c r="L27" s="27"/>
-      <c r="M27" s="27"/>
+      <c r="K27" s="22"/>
+      <c r="L27" s="22"/>
+      <c r="M27" s="22"/>
     </row>
     <row r="28" spans="2:13">
       <c r="B28" s="4"/>
@@ -1437,10 +1189,10 @@
       <c r="G28" s="5"/>
       <c r="H28" s="5"/>
       <c r="I28" s="4"/>
-      <c r="J28" s="18"/>
-      <c r="K28" s="18"/>
-      <c r="L28" s="18"/>
-      <c r="M28" s="18"/>
+      <c r="J28" s="14"/>
+      <c r="K28" s="14"/>
+      <c r="L28" s="14"/>
+      <c r="M28" s="14"/>
     </row>
     <row r="29" spans="2:13">
       <c r="B29" s="4"/>
@@ -1451,10 +1203,10 @@
       <c r="G29" s="5"/>
       <c r="H29" s="5"/>
       <c r="I29" s="4"/>
-      <c r="J29" s="28"/>
-      <c r="K29" s="28"/>
-      <c r="L29" s="28"/>
-      <c r="M29" s="28"/>
+      <c r="J29" s="15"/>
+      <c r="K29" s="15"/>
+      <c r="L29" s="15"/>
+      <c r="M29" s="15"/>
     </row>
     <row r="30" spans="2:13" ht="15">
       <c r="B30" s="4"/>
@@ -1465,12 +1217,12 @@
       <c r="G30" s="5"/>
       <c r="H30" s="5"/>
       <c r="I30" s="4"/>
-      <c r="J30" s="29" t="s">
+      <c r="J30" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="K30" s="29"/>
-      <c r="L30" s="29"/>
-      <c r="M30" s="29"/>
+      <c r="K30" s="23"/>
+      <c r="L30" s="23"/>
+      <c r="M30" s="23"/>
     </row>
     <row r="31" spans="2:13">
       <c r="B31" s="4"/>
@@ -1481,10 +1233,10 @@
       <c r="G31" s="5"/>
       <c r="H31" s="5"/>
       <c r="I31" s="4"/>
-      <c r="J31" s="18"/>
-      <c r="K31" s="18"/>
-      <c r="L31" s="18"/>
-      <c r="M31" s="18"/>
+      <c r="J31" s="14"/>
+      <c r="K31" s="14"/>
+      <c r="L31" s="14"/>
+      <c r="M31" s="14"/>
     </row>
     <row r="32" spans="2:13" ht="15">
       <c r="B32" s="4"/>
@@ -1525,10 +1277,10 @@
       <c r="G34" s="5"/>
       <c r="H34" s="5"/>
       <c r="I34" s="4"/>
-      <c r="J34" s="24"/>
-      <c r="K34" s="24"/>
-      <c r="L34" s="24"/>
-      <c r="M34" s="24"/>
+      <c r="J34" s="20"/>
+      <c r="K34" s="20"/>
+      <c r="L34" s="20"/>
+      <c r="M34" s="20"/>
     </row>
     <row r="35" spans="2:13" ht="14.25">
       <c r="B35" s="4"/>
@@ -1539,12 +1291,12 @@
       <c r="G35" s="5"/>
       <c r="H35" s="5"/>
       <c r="I35" s="4"/>
-      <c r="J35" s="22" t="s">
+      <c r="J35" s="32" t="s">
         <v>3</v>
       </c>
-      <c r="K35" s="22"/>
-      <c r="L35" s="22"/>
-      <c r="M35" s="22"/>
+      <c r="K35" s="32"/>
+      <c r="L35" s="32"/>
+      <c r="M35" s="32"/>
     </row>
     <row r="36" spans="2:13">
       <c r="B36" s="4"/>
@@ -1555,10 +1307,10 @@
       <c r="G36" s="5"/>
       <c r="H36" s="5"/>
       <c r="I36" s="4"/>
-      <c r="J36" s="24"/>
-      <c r="K36" s="24"/>
-      <c r="L36" s="24"/>
-      <c r="M36" s="24"/>
+      <c r="J36" s="20"/>
+      <c r="K36" s="20"/>
+      <c r="L36" s="20"/>
+      <c r="M36" s="20"/>
     </row>
     <row r="37" spans="2:13">
       <c r="B37" s="4"/>
@@ -1569,10 +1321,10 @@
       <c r="G37" s="5"/>
       <c r="H37" s="5"/>
       <c r="I37" s="4"/>
-      <c r="J37" s="24"/>
-      <c r="K37" s="24"/>
-      <c r="L37" s="24"/>
-      <c r="M37" s="24"/>
+      <c r="J37" s="20"/>
+      <c r="K37" s="20"/>
+      <c r="L37" s="20"/>
+      <c r="M37" s="20"/>
     </row>
     <row r="38" spans="2:13">
       <c r="B38" s="4"/>
@@ -1583,10 +1335,10 @@
       <c r="G38" s="5"/>
       <c r="H38" s="5"/>
       <c r="I38" s="4"/>
-      <c r="J38" s="24"/>
-      <c r="K38" s="24"/>
-      <c r="L38" s="24"/>
-      <c r="M38" s="24"/>
+      <c r="J38" s="20"/>
+      <c r="K38" s="20"/>
+      <c r="L38" s="20"/>
+      <c r="M38" s="20"/>
     </row>
     <row r="39" spans="2:13">
       <c r="B39" s="4"/>
@@ -1597,10 +1349,10 @@
       <c r="G39" s="5"/>
       <c r="H39" s="5"/>
       <c r="I39" s="4"/>
-      <c r="J39" s="32"/>
-      <c r="K39" s="32"/>
-      <c r="L39" s="32"/>
-      <c r="M39" s="32"/>
+      <c r="J39" s="27"/>
+      <c r="K39" s="27"/>
+      <c r="L39" s="27"/>
+      <c r="M39" s="27"/>
     </row>
     <row r="40" spans="2:13">
       <c r="B40" s="4"/>
@@ -1611,10 +1363,10 @@
       <c r="G40" s="5"/>
       <c r="H40" s="5"/>
       <c r="I40" s="4"/>
-      <c r="J40" s="33"/>
-      <c r="K40" s="33"/>
-      <c r="L40" s="33"/>
-      <c r="M40" s="33"/>
+      <c r="J40" s="28"/>
+      <c r="K40" s="28"/>
+      <c r="L40" s="28"/>
+      <c r="M40" s="28"/>
     </row>
     <row r="41" spans="2:13">
       <c r="B41" s="4"/>
@@ -1625,10 +1377,10 @@
       <c r="G41" s="5"/>
       <c r="H41" s="5"/>
       <c r="I41" s="4"/>
-      <c r="J41" s="18"/>
-      <c r="K41" s="18"/>
-      <c r="L41" s="18"/>
-      <c r="M41" s="18"/>
+      <c r="J41" s="14"/>
+      <c r="K41" s="14"/>
+      <c r="L41" s="14"/>
+      <c r="M41" s="14"/>
     </row>
     <row r="42" spans="2:13">
       <c r="B42" s="4"/>
@@ -1639,10 +1391,10 @@
       <c r="G42" s="5"/>
       <c r="H42" s="5"/>
       <c r="I42" s="4"/>
-      <c r="J42" s="18"/>
-      <c r="K42" s="18"/>
-      <c r="L42" s="18"/>
-      <c r="M42" s="18"/>
+      <c r="J42" s="14"/>
+      <c r="K42" s="14"/>
+      <c r="L42" s="14"/>
+      <c r="M42" s="14"/>
     </row>
     <row r="43" spans="2:13">
       <c r="B43" s="4"/>
@@ -1653,13 +1405,13 @@
       <c r="G43" s="5"/>
       <c r="H43" s="5"/>
       <c r="I43" s="4"/>
-      <c r="J43" s="24" t="str">
+      <c r="J43" s="20" t="str">
         <f>J20</f>
         <v>2026.2.17　作業</v>
       </c>
-      <c r="K43" s="24"/>
-      <c r="L43" s="24"/>
-      <c r="M43" s="24"/>
+      <c r="K43" s="20"/>
+      <c r="L43" s="20"/>
+      <c r="M43" s="20"/>
     </row>
     <row r="44" spans="2:13">
       <c r="B44" s="4"/>
@@ -1670,10 +1422,10 @@
       <c r="G44" s="5"/>
       <c r="H44" s="5"/>
       <c r="I44" s="4"/>
-      <c r="J44" s="25"/>
-      <c r="K44" s="25"/>
-      <c r="L44" s="25"/>
-      <c r="M44" s="25"/>
+      <c r="J44" s="21"/>
+      <c r="K44" s="21"/>
+      <c r="L44" s="21"/>
+      <c r="M44" s="21"/>
     </row>
     <row r="45" spans="2:13" ht="14.25" customHeight="1">
       <c r="B45" s="6"/>
@@ -1711,10 +1463,10 @@
       <c r="G47" s="3"/>
       <c r="H47" s="3"/>
       <c r="I47" s="2"/>
-      <c r="J47" s="26"/>
-      <c r="K47" s="26"/>
-      <c r="L47" s="26"/>
-      <c r="M47" s="26"/>
+      <c r="J47" s="29"/>
+      <c r="K47" s="29"/>
+      <c r="L47" s="29"/>
+      <c r="M47" s="29"/>
     </row>
     <row r="48" spans="2:13" ht="15">
       <c r="B48" s="4"/>
@@ -1725,13 +1477,13 @@
       <c r="G48" s="5"/>
       <c r="H48" s="5"/>
       <c r="I48" s="4"/>
-      <c r="J48" s="15" t="str">
+      <c r="J48" s="17" t="str">
         <f>J2</f>
         <v>ミニチュアリレー　#LCM</v>
       </c>
-      <c r="K48" s="15"/>
-      <c r="L48" s="15"/>
-      <c r="M48" s="15"/>
+      <c r="K48" s="17"/>
+      <c r="L48" s="17"/>
+      <c r="M48" s="17"/>
     </row>
     <row r="49" spans="2:13" ht="15">
       <c r="B49" s="4"/>
@@ -1742,10 +1494,10 @@
       <c r="G49" s="5"/>
       <c r="H49" s="5"/>
       <c r="I49" s="4"/>
-      <c r="J49" s="17"/>
-      <c r="K49" s="17"/>
-      <c r="L49" s="17"/>
-      <c r="M49" s="17"/>
+      <c r="J49" s="18"/>
+      <c r="K49" s="18"/>
+      <c r="L49" s="18"/>
+      <c r="M49" s="18"/>
     </row>
     <row r="50" spans="2:13" ht="15">
       <c r="B50" s="4"/>
@@ -1756,12 +1508,12 @@
       <c r="G50" s="5"/>
       <c r="H50" s="5"/>
       <c r="I50" s="4"/>
-      <c r="J50" s="27" t="s">
+      <c r="J50" s="22" t="s">
         <v>8</v>
       </c>
-      <c r="K50" s="27"/>
-      <c r="L50" s="27"/>
-      <c r="M50" s="27"/>
+      <c r="K50" s="22"/>
+      <c r="L50" s="22"/>
+      <c r="M50" s="22"/>
     </row>
     <row r="51" spans="2:13">
       <c r="B51" s="4"/>
@@ -1772,10 +1524,10 @@
       <c r="G51" s="5"/>
       <c r="H51" s="5"/>
       <c r="I51" s="4"/>
-      <c r="J51" s="18"/>
-      <c r="K51" s="18"/>
-      <c r="L51" s="18"/>
-      <c r="M51" s="18"/>
+      <c r="J51" s="14"/>
+      <c r="K51" s="14"/>
+      <c r="L51" s="14"/>
+      <c r="M51" s="14"/>
     </row>
     <row r="52" spans="2:13">
       <c r="B52" s="4"/>
@@ -1786,10 +1538,10 @@
       <c r="G52" s="5"/>
       <c r="H52" s="5"/>
       <c r="I52" s="4"/>
-      <c r="J52" s="34"/>
-      <c r="K52" s="34"/>
-      <c r="L52" s="34"/>
-      <c r="M52" s="34"/>
+      <c r="J52" s="19"/>
+      <c r="K52" s="19"/>
+      <c r="L52" s="19"/>
+      <c r="M52" s="19"/>
     </row>
     <row r="53" spans="2:13" ht="15">
       <c r="B53" s="4"/>
@@ -1800,12 +1552,12 @@
       <c r="G53" s="5"/>
       <c r="H53" s="5"/>
       <c r="I53" s="4"/>
-      <c r="J53" s="29" t="s">
+      <c r="J53" s="23" t="s">
         <v>6</v>
       </c>
-      <c r="K53" s="29"/>
-      <c r="L53" s="29"/>
-      <c r="M53" s="29"/>
+      <c r="K53" s="23"/>
+      <c r="L53" s="23"/>
+      <c r="M53" s="23"/>
     </row>
     <row r="54" spans="2:13">
       <c r="B54" s="4"/>
@@ -1816,10 +1568,10 @@
       <c r="G54" s="5"/>
       <c r="H54" s="5"/>
       <c r="I54" s="4"/>
-      <c r="J54" s="35"/>
-      <c r="K54" s="35"/>
-      <c r="L54" s="35"/>
-      <c r="M54" s="35"/>
+      <c r="J54" s="24"/>
+      <c r="K54" s="24"/>
+      <c r="L54" s="24"/>
+      <c r="M54" s="24"/>
     </row>
     <row r="55" spans="2:13">
       <c r="B55" s="4"/>
@@ -1830,10 +1582,10 @@
       <c r="G55" s="5"/>
       <c r="H55" s="5"/>
       <c r="I55" s="4"/>
-      <c r="J55" s="18"/>
-      <c r="K55" s="18"/>
-      <c r="L55" s="18"/>
-      <c r="M55" s="18"/>
+      <c r="J55" s="14"/>
+      <c r="K55" s="14"/>
+      <c r="L55" s="14"/>
+      <c r="M55" s="14"/>
     </row>
     <row r="56" spans="2:13" ht="15">
       <c r="B56" s="4"/>
@@ -1844,12 +1596,12 @@
       <c r="G56" s="5"/>
       <c r="H56" s="5"/>
       <c r="I56" s="4"/>
-      <c r="J56" s="36" t="s">
+      <c r="J56" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="K56" s="36"/>
-      <c r="L56" s="36"/>
-      <c r="M56" s="36"/>
+      <c r="K56" s="25"/>
+      <c r="L56" s="25"/>
+      <c r="M56" s="25"/>
     </row>
     <row r="57" spans="2:13">
       <c r="B57" s="4"/>
@@ -1860,10 +1612,10 @@
       <c r="G57" s="5"/>
       <c r="H57" s="5"/>
       <c r="I57" s="4"/>
-      <c r="J57" s="23"/>
-      <c r="K57" s="23"/>
-      <c r="L57" s="23"/>
-      <c r="M57" s="23"/>
+      <c r="J57" s="26"/>
+      <c r="K57" s="26"/>
+      <c r="L57" s="26"/>
+      <c r="M57" s="26"/>
     </row>
     <row r="58" spans="2:13">
       <c r="B58" s="4"/>
@@ -1874,10 +1626,10 @@
       <c r="G58" s="5"/>
       <c r="H58" s="5"/>
       <c r="I58" s="4"/>
-      <c r="J58" s="24"/>
-      <c r="K58" s="24"/>
-      <c r="L58" s="24"/>
-      <c r="M58" s="24"/>
+      <c r="J58" s="20"/>
+      <c r="K58" s="20"/>
+      <c r="L58" s="20"/>
+      <c r="M58" s="20"/>
     </row>
     <row r="59" spans="2:13">
       <c r="B59" s="4"/>
@@ -1888,10 +1640,10 @@
       <c r="G59" s="5"/>
       <c r="H59" s="5"/>
       <c r="I59" s="4"/>
-      <c r="J59" s="18"/>
-      <c r="K59" s="18"/>
-      <c r="L59" s="18"/>
-      <c r="M59" s="18"/>
+      <c r="J59" s="14"/>
+      <c r="K59" s="14"/>
+      <c r="L59" s="14"/>
+      <c r="M59" s="14"/>
     </row>
     <row r="60" spans="2:13">
       <c r="B60" s="4"/>
@@ -1902,10 +1654,10 @@
       <c r="G60" s="5"/>
       <c r="H60" s="5"/>
       <c r="I60" s="4"/>
-      <c r="J60" s="18"/>
-      <c r="K60" s="18"/>
-      <c r="L60" s="18"/>
-      <c r="M60" s="18"/>
+      <c r="J60" s="14"/>
+      <c r="K60" s="14"/>
+      <c r="L60" s="14"/>
+      <c r="M60" s="14"/>
     </row>
     <row r="61" spans="2:13">
       <c r="B61" s="4"/>
@@ -1916,10 +1668,10 @@
       <c r="G61" s="5"/>
       <c r="H61" s="5"/>
       <c r="I61" s="4"/>
-      <c r="J61" s="18"/>
-      <c r="K61" s="18"/>
-      <c r="L61" s="18"/>
-      <c r="M61" s="18"/>
+      <c r="J61" s="14"/>
+      <c r="K61" s="14"/>
+      <c r="L61" s="14"/>
+      <c r="M61" s="14"/>
     </row>
     <row r="62" spans="2:13">
       <c r="B62" s="4"/>
@@ -1930,10 +1682,10 @@
       <c r="G62" s="5"/>
       <c r="H62" s="5"/>
       <c r="I62" s="4"/>
-      <c r="J62" s="18"/>
-      <c r="K62" s="18"/>
-      <c r="L62" s="18"/>
-      <c r="M62" s="18"/>
+      <c r="J62" s="14"/>
+      <c r="K62" s="14"/>
+      <c r="L62" s="14"/>
+      <c r="M62" s="14"/>
     </row>
     <row r="63" spans="2:13">
       <c r="B63" s="4"/>
@@ -1944,10 +1696,10 @@
       <c r="G63" s="5"/>
       <c r="H63" s="5"/>
       <c r="I63" s="4"/>
-      <c r="J63" s="18"/>
-      <c r="K63" s="18"/>
-      <c r="L63" s="18"/>
-      <c r="M63" s="18"/>
+      <c r="J63" s="14"/>
+      <c r="K63" s="14"/>
+      <c r="L63" s="14"/>
+      <c r="M63" s="14"/>
     </row>
     <row r="64" spans="2:13">
       <c r="B64" s="4"/>
@@ -1958,10 +1710,10 @@
       <c r="G64" s="5"/>
       <c r="H64" s="5"/>
       <c r="I64" s="4"/>
-      <c r="J64" s="18"/>
-      <c r="K64" s="18"/>
-      <c r="L64" s="18"/>
-      <c r="M64" s="18"/>
+      <c r="J64" s="14"/>
+      <c r="K64" s="14"/>
+      <c r="L64" s="14"/>
+      <c r="M64" s="14"/>
     </row>
     <row r="65" spans="2:13">
       <c r="B65" s="4"/>
@@ -1972,10 +1724,10 @@
       <c r="G65" s="5"/>
       <c r="H65" s="5"/>
       <c r="I65" s="4"/>
-      <c r="J65" s="18"/>
-      <c r="K65" s="18"/>
-      <c r="L65" s="18"/>
-      <c r="M65" s="18"/>
+      <c r="J65" s="14"/>
+      <c r="K65" s="14"/>
+      <c r="L65" s="14"/>
+      <c r="M65" s="14"/>
     </row>
     <row r="66" spans="2:13">
       <c r="B66" s="4"/>
@@ -1986,13 +1738,13 @@
       <c r="G66" s="5"/>
       <c r="H66" s="5"/>
       <c r="I66" s="4"/>
-      <c r="J66" s="24" t="str">
+      <c r="J66" s="20" t="str">
         <f>J20</f>
         <v>2026.2.17　作業</v>
       </c>
-      <c r="K66" s="24"/>
-      <c r="L66" s="24"/>
-      <c r="M66" s="24"/>
+      <c r="K66" s="20"/>
+      <c r="L66" s="20"/>
+      <c r="M66" s="20"/>
     </row>
     <row r="67" spans="2:13">
       <c r="B67" s="4"/>
@@ -2003,10 +1755,10 @@
       <c r="G67" s="5"/>
       <c r="H67" s="5"/>
       <c r="I67" s="4"/>
-      <c r="J67" s="25"/>
-      <c r="K67" s="25"/>
-      <c r="L67" s="25"/>
-      <c r="M67" s="25"/>
+      <c r="J67" s="21"/>
+      <c r="K67" s="21"/>
+      <c r="L67" s="21"/>
+      <c r="M67" s="21"/>
     </row>
     <row r="68" spans="2:13" ht="14.25" customHeight="1">
       <c r="B68" s="6"/>
@@ -2045,10 +1797,10 @@
       <c r="G70" s="5"/>
       <c r="H70" s="5"/>
       <c r="I70" s="4"/>
-      <c r="J70" s="15"/>
-      <c r="K70" s="15"/>
-      <c r="L70" s="15"/>
-      <c r="M70" s="15"/>
+      <c r="J70" s="17"/>
+      <c r="K70" s="17"/>
+      <c r="L70" s="17"/>
+      <c r="M70" s="17"/>
     </row>
     <row r="71" spans="2:13" ht="15">
       <c r="B71" s="4"/>
@@ -2059,10 +1811,10 @@
       <c r="G71" s="5"/>
       <c r="H71" s="5"/>
       <c r="I71" s="4"/>
-      <c r="J71" s="17"/>
-      <c r="K71" s="17"/>
-      <c r="L71" s="17"/>
-      <c r="M71" s="17"/>
+      <c r="J71" s="18"/>
+      <c r="K71" s="18"/>
+      <c r="L71" s="18"/>
+      <c r="M71" s="18"/>
     </row>
     <row r="72" spans="2:13">
       <c r="B72" s="4"/>
@@ -2073,10 +1825,10 @@
       <c r="G72" s="5"/>
       <c r="H72" s="5"/>
       <c r="I72" s="4"/>
-      <c r="J72" s="18"/>
-      <c r="K72" s="18"/>
-      <c r="L72" s="18"/>
-      <c r="M72" s="18"/>
+      <c r="J72" s="14"/>
+      <c r="K72" s="14"/>
+      <c r="L72" s="14"/>
+      <c r="M72" s="14"/>
     </row>
     <row r="73" spans="2:13">
       <c r="B73" s="4"/>
@@ -2087,10 +1839,10 @@
       <c r="G73" s="5"/>
       <c r="H73" s="5"/>
       <c r="I73" s="4"/>
-      <c r="J73" s="18"/>
-      <c r="K73" s="18"/>
-      <c r="L73" s="18"/>
-      <c r="M73" s="18"/>
+      <c r="J73" s="14"/>
+      <c r="K73" s="14"/>
+      <c r="L73" s="14"/>
+      <c r="M73" s="14"/>
     </row>
     <row r="74" spans="2:13">
       <c r="B74" s="4"/>
@@ -2101,10 +1853,10 @@
       <c r="G74" s="5"/>
       <c r="H74" s="5"/>
       <c r="I74" s="4"/>
-      <c r="J74" s="34"/>
-      <c r="K74" s="34"/>
-      <c r="L74" s="34"/>
-      <c r="M74" s="34"/>
+      <c r="J74" s="19"/>
+      <c r="K74" s="19"/>
+      <c r="L74" s="19"/>
+      <c r="M74" s="19"/>
     </row>
     <row r="75" spans="2:13">
       <c r="B75" s="4"/>
@@ -2115,10 +1867,10 @@
       <c r="G75" s="5"/>
       <c r="H75" s="5"/>
       <c r="I75" s="4"/>
-      <c r="J75" s="28"/>
-      <c r="K75" s="28"/>
-      <c r="L75" s="28"/>
-      <c r="M75" s="28"/>
+      <c r="J75" s="15"/>
+      <c r="K75" s="15"/>
+      <c r="L75" s="15"/>
+      <c r="M75" s="15"/>
     </row>
     <row r="76" spans="2:13">
       <c r="B76" s="4"/>
@@ -2129,10 +1881,10 @@
       <c r="G76" s="5"/>
       <c r="H76" s="5"/>
       <c r="I76" s="4"/>
-      <c r="J76" s="18"/>
-      <c r="K76" s="18"/>
-      <c r="L76" s="18"/>
-      <c r="M76" s="18"/>
+      <c r="J76" s="14"/>
+      <c r="K76" s="14"/>
+      <c r="L76" s="14"/>
+      <c r="M76" s="14"/>
     </row>
     <row r="77" spans="2:13">
       <c r="B77" s="4"/>
@@ -2143,10 +1895,10 @@
       <c r="G77" s="5"/>
       <c r="H77" s="5"/>
       <c r="I77" s="4"/>
-      <c r="J77" s="18"/>
-      <c r="K77" s="18"/>
-      <c r="L77" s="18"/>
-      <c r="M77" s="18"/>
+      <c r="J77" s="14"/>
+      <c r="K77" s="14"/>
+      <c r="L77" s="14"/>
+      <c r="M77" s="14"/>
     </row>
     <row r="78" spans="2:13">
       <c r="B78" s="4"/>
@@ -2157,10 +1909,10 @@
       <c r="G78" s="5"/>
       <c r="H78" s="5"/>
       <c r="I78" s="4"/>
-      <c r="J78" s="18"/>
-      <c r="K78" s="18"/>
-      <c r="L78" s="18"/>
-      <c r="M78" s="18"/>
+      <c r="J78" s="14"/>
+      <c r="K78" s="14"/>
+      <c r="L78" s="14"/>
+      <c r="M78" s="14"/>
     </row>
     <row r="79" spans="2:13">
       <c r="B79" s="4"/>
@@ -2171,10 +1923,10 @@
       <c r="G79" s="5"/>
       <c r="H79" s="5"/>
       <c r="I79" s="4"/>
-      <c r="J79" s="18"/>
-      <c r="K79" s="18"/>
-      <c r="L79" s="18"/>
-      <c r="M79" s="18"/>
+      <c r="J79" s="14"/>
+      <c r="K79" s="14"/>
+      <c r="L79" s="14"/>
+      <c r="M79" s="14"/>
     </row>
     <row r="80" spans="2:13">
       <c r="B80" s="4"/>
@@ -2185,10 +1937,10 @@
       <c r="G80" s="5"/>
       <c r="H80" s="5"/>
       <c r="I80" s="4"/>
-      <c r="J80" s="18"/>
-      <c r="K80" s="18"/>
-      <c r="L80" s="18"/>
-      <c r="M80" s="18"/>
+      <c r="J80" s="14"/>
+      <c r="K80" s="14"/>
+      <c r="L80" s="14"/>
+      <c r="M80" s="14"/>
     </row>
     <row r="81" spans="2:13">
       <c r="B81" s="4"/>
@@ -2199,10 +1951,10 @@
       <c r="G81" s="5"/>
       <c r="H81" s="5"/>
       <c r="I81" s="4"/>
-      <c r="J81" s="18"/>
-      <c r="K81" s="18"/>
-      <c r="L81" s="18"/>
-      <c r="M81" s="18"/>
+      <c r="J81" s="14"/>
+      <c r="K81" s="14"/>
+      <c r="L81" s="14"/>
+      <c r="M81" s="14"/>
     </row>
     <row r="82" spans="2:13">
       <c r="B82" s="4"/>
@@ -2213,10 +1965,10 @@
       <c r="G82" s="5"/>
       <c r="H82" s="5"/>
       <c r="I82" s="4"/>
-      <c r="J82" s="18"/>
-      <c r="K82" s="18"/>
-      <c r="L82" s="18"/>
-      <c r="M82" s="18"/>
+      <c r="J82" s="14"/>
+      <c r="K82" s="14"/>
+      <c r="L82" s="14"/>
+      <c r="M82" s="14"/>
     </row>
     <row r="83" spans="2:13">
       <c r="B83" s="4"/>
@@ -2227,10 +1979,10 @@
       <c r="G83" s="5"/>
       <c r="H83" s="5"/>
       <c r="I83" s="4"/>
-      <c r="J83" s="18"/>
-      <c r="K83" s="18"/>
-      <c r="L83" s="18"/>
-      <c r="M83" s="18"/>
+      <c r="J83" s="14"/>
+      <c r="K83" s="14"/>
+      <c r="L83" s="14"/>
+      <c r="M83" s="14"/>
     </row>
     <row r="84" spans="2:13">
       <c r="B84" s="4"/>
@@ -2241,10 +1993,10 @@
       <c r="G84" s="5"/>
       <c r="H84" s="5"/>
       <c r="I84" s="4"/>
-      <c r="J84" s="18"/>
-      <c r="K84" s="18"/>
-      <c r="L84" s="18"/>
-      <c r="M84" s="18"/>
+      <c r="J84" s="14"/>
+      <c r="K84" s="14"/>
+      <c r="L84" s="14"/>
+      <c r="M84" s="14"/>
     </row>
     <row r="85" spans="2:13">
       <c r="B85" s="4"/>
@@ -2255,10 +2007,10 @@
       <c r="G85" s="5"/>
       <c r="H85" s="5"/>
       <c r="I85" s="4"/>
-      <c r="J85" s="18"/>
-      <c r="K85" s="18"/>
-      <c r="L85" s="18"/>
-      <c r="M85" s="18"/>
+      <c r="J85" s="14"/>
+      <c r="K85" s="14"/>
+      <c r="L85" s="14"/>
+      <c r="M85" s="14"/>
     </row>
     <row r="86" spans="2:13">
       <c r="B86" s="4"/>
@@ -2269,10 +2021,10 @@
       <c r="G86" s="5"/>
       <c r="H86" s="5"/>
       <c r="I86" s="4"/>
-      <c r="J86" s="18"/>
-      <c r="K86" s="18"/>
-      <c r="L86" s="18"/>
-      <c r="M86" s="18"/>
+      <c r="J86" s="14"/>
+      <c r="K86" s="14"/>
+      <c r="L86" s="14"/>
+      <c r="M86" s="14"/>
     </row>
     <row r="87" spans="2:13">
       <c r="B87" s="4"/>
@@ -2283,10 +2035,10 @@
       <c r="G87" s="5"/>
       <c r="H87" s="5"/>
       <c r="I87" s="4"/>
-      <c r="J87" s="18"/>
-      <c r="K87" s="18"/>
-      <c r="L87" s="18"/>
-      <c r="M87" s="18"/>
+      <c r="J87" s="14"/>
+      <c r="K87" s="14"/>
+      <c r="L87" s="14"/>
+      <c r="M87" s="14"/>
     </row>
     <row r="88" spans="2:13">
       <c r="B88" s="4"/>
@@ -2297,10 +2049,10 @@
       <c r="G88" s="5"/>
       <c r="H88" s="5"/>
       <c r="I88" s="4"/>
-      <c r="J88" s="18"/>
-      <c r="K88" s="18"/>
-      <c r="L88" s="18"/>
-      <c r="M88" s="18"/>
+      <c r="J88" s="14"/>
+      <c r="K88" s="14"/>
+      <c r="L88" s="14"/>
+      <c r="M88" s="14"/>
     </row>
     <row r="89" spans="2:13">
       <c r="B89" s="4"/>
@@ -2311,10 +2063,10 @@
       <c r="G89" s="5"/>
       <c r="H89" s="5"/>
       <c r="I89" s="4"/>
-      <c r="J89" s="37"/>
-      <c r="K89" s="37"/>
-      <c r="L89" s="37"/>
-      <c r="M89" s="37"/>
+      <c r="J89" s="16"/>
+      <c r="K89" s="16"/>
+      <c r="L89" s="16"/>
+      <c r="M89" s="16"/>
     </row>
     <row r="90" spans="2:13" ht="14.25" customHeight="1">
       <c r="B90" s="6"/>
@@ -2366,10 +2118,10 @@
       <c r="G93" s="5"/>
       <c r="H93" s="5"/>
       <c r="I93" s="4"/>
-      <c r="J93" s="15"/>
-      <c r="K93" s="15"/>
-      <c r="L93" s="15"/>
-      <c r="M93" s="15"/>
+      <c r="J93" s="17"/>
+      <c r="K93" s="17"/>
+      <c r="L93" s="17"/>
+      <c r="M93" s="17"/>
     </row>
     <row r="94" spans="2:13" ht="15">
       <c r="B94" s="4"/>
@@ -2380,10 +2132,10 @@
       <c r="G94" s="5"/>
       <c r="H94" s="5"/>
       <c r="I94" s="4"/>
-      <c r="J94" s="17"/>
-      <c r="K94" s="17"/>
-      <c r="L94" s="17"/>
-      <c r="M94" s="17"/>
+      <c r="J94" s="18"/>
+      <c r="K94" s="18"/>
+      <c r="L94" s="18"/>
+      <c r="M94" s="18"/>
     </row>
     <row r="95" spans="2:13">
       <c r="B95" s="4"/>
@@ -2394,10 +2146,10 @@
       <c r="G95" s="5"/>
       <c r="H95" s="5"/>
       <c r="I95" s="4"/>
-      <c r="J95" s="18"/>
-      <c r="K95" s="18"/>
-      <c r="L95" s="18"/>
-      <c r="M95" s="18"/>
+      <c r="J95" s="14"/>
+      <c r="K95" s="14"/>
+      <c r="L95" s="14"/>
+      <c r="M95" s="14"/>
     </row>
     <row r="96" spans="2:13">
       <c r="B96" s="4"/>
@@ -2408,10 +2160,10 @@
       <c r="G96" s="5"/>
       <c r="H96" s="5"/>
       <c r="I96" s="4"/>
-      <c r="J96" s="18"/>
-      <c r="K96" s="18"/>
-      <c r="L96" s="18"/>
-      <c r="M96" s="18"/>
+      <c r="J96" s="14"/>
+      <c r="K96" s="14"/>
+      <c r="L96" s="14"/>
+      <c r="M96" s="14"/>
     </row>
     <row r="97" spans="2:13">
       <c r="B97" s="4"/>
@@ -2422,10 +2174,10 @@
       <c r="G97" s="5"/>
       <c r="H97" s="5"/>
       <c r="I97" s="4"/>
-      <c r="J97" s="28"/>
-      <c r="K97" s="28"/>
-      <c r="L97" s="28"/>
-      <c r="M97" s="28"/>
+      <c r="J97" s="15"/>
+      <c r="K97" s="15"/>
+      <c r="L97" s="15"/>
+      <c r="M97" s="15"/>
     </row>
     <row r="98" spans="2:13">
       <c r="B98" s="4"/>
@@ -2436,10 +2188,10 @@
       <c r="G98" s="5"/>
       <c r="H98" s="5"/>
       <c r="I98" s="4"/>
-      <c r="J98" s="28"/>
-      <c r="K98" s="28"/>
-      <c r="L98" s="28"/>
-      <c r="M98" s="28"/>
+      <c r="J98" s="15"/>
+      <c r="K98" s="15"/>
+      <c r="L98" s="15"/>
+      <c r="M98" s="15"/>
     </row>
     <row r="99" spans="2:13">
       <c r="B99" s="4"/>
@@ -2450,10 +2202,10 @@
       <c r="G99" s="5"/>
       <c r="H99" s="5"/>
       <c r="I99" s="4"/>
-      <c r="J99" s="18"/>
-      <c r="K99" s="18"/>
-      <c r="L99" s="18"/>
-      <c r="M99" s="18"/>
+      <c r="J99" s="14"/>
+      <c r="K99" s="14"/>
+      <c r="L99" s="14"/>
+      <c r="M99" s="14"/>
     </row>
     <row r="100" spans="2:13">
       <c r="B100" s="4"/>
@@ -2464,10 +2216,10 @@
       <c r="G100" s="5"/>
       <c r="H100" s="5"/>
       <c r="I100" s="4"/>
-      <c r="J100" s="18"/>
-      <c r="K100" s="18"/>
-      <c r="L100" s="18"/>
-      <c r="M100" s="18"/>
+      <c r="J100" s="14"/>
+      <c r="K100" s="14"/>
+      <c r="L100" s="14"/>
+      <c r="M100" s="14"/>
     </row>
     <row r="101" spans="2:13">
       <c r="B101" s="4"/>
@@ -2478,10 +2230,10 @@
       <c r="G101" s="5"/>
       <c r="H101" s="5"/>
       <c r="I101" s="4"/>
-      <c r="J101" s="18"/>
-      <c r="K101" s="18"/>
-      <c r="L101" s="18"/>
-      <c r="M101" s="18"/>
+      <c r="J101" s="14"/>
+      <c r="K101" s="14"/>
+      <c r="L101" s="14"/>
+      <c r="M101" s="14"/>
     </row>
     <row r="102" spans="2:13">
       <c r="B102" s="4"/>
@@ -2492,10 +2244,10 @@
       <c r="G102" s="5"/>
       <c r="H102" s="5"/>
       <c r="I102" s="4"/>
-      <c r="J102" s="18"/>
-      <c r="K102" s="18"/>
-      <c r="L102" s="18"/>
-      <c r="M102" s="18"/>
+      <c r="J102" s="14"/>
+      <c r="K102" s="14"/>
+      <c r="L102" s="14"/>
+      <c r="M102" s="14"/>
     </row>
     <row r="103" spans="2:13">
       <c r="B103" s="4"/>
@@ -2506,10 +2258,10 @@
       <c r="G103" s="5"/>
       <c r="H103" s="5"/>
       <c r="I103" s="4"/>
-      <c r="J103" s="18"/>
-      <c r="K103" s="18"/>
-      <c r="L103" s="18"/>
-      <c r="M103" s="18"/>
+      <c r="J103" s="14"/>
+      <c r="K103" s="14"/>
+      <c r="L103" s="14"/>
+      <c r="M103" s="14"/>
     </row>
     <row r="104" spans="2:13">
       <c r="B104" s="4"/>
@@ -2520,10 +2272,10 @@
       <c r="G104" s="5"/>
       <c r="H104" s="5"/>
       <c r="I104" s="4"/>
-      <c r="J104" s="18"/>
-      <c r="K104" s="18"/>
-      <c r="L104" s="18"/>
-      <c r="M104" s="18"/>
+      <c r="J104" s="14"/>
+      <c r="K104" s="14"/>
+      <c r="L104" s="14"/>
+      <c r="M104" s="14"/>
     </row>
     <row r="105" spans="2:13">
       <c r="B105" s="4"/>
@@ -2534,10 +2286,10 @@
       <c r="G105" s="5"/>
       <c r="H105" s="5"/>
       <c r="I105" s="4"/>
-      <c r="J105" s="18"/>
-      <c r="K105" s="18"/>
-      <c r="L105" s="18"/>
-      <c r="M105" s="18"/>
+      <c r="J105" s="14"/>
+      <c r="K105" s="14"/>
+      <c r="L105" s="14"/>
+      <c r="M105" s="14"/>
     </row>
     <row r="106" spans="2:13">
       <c r="B106" s="4"/>
@@ -2548,10 +2300,10 @@
       <c r="G106" s="5"/>
       <c r="H106" s="5"/>
       <c r="I106" s="4"/>
-      <c r="J106" s="18"/>
-      <c r="K106" s="18"/>
-      <c r="L106" s="18"/>
-      <c r="M106" s="18"/>
+      <c r="J106" s="14"/>
+      <c r="K106" s="14"/>
+      <c r="L106" s="14"/>
+      <c r="M106" s="14"/>
     </row>
     <row r="107" spans="2:13">
       <c r="B107" s="4"/>
@@ -2562,10 +2314,10 @@
       <c r="G107" s="5"/>
       <c r="H107" s="5"/>
       <c r="I107" s="4"/>
-      <c r="J107" s="18"/>
-      <c r="K107" s="18"/>
-      <c r="L107" s="18"/>
-      <c r="M107" s="18"/>
+      <c r="J107" s="14"/>
+      <c r="K107" s="14"/>
+      <c r="L107" s="14"/>
+      <c r="M107" s="14"/>
     </row>
     <row r="108" spans="2:13">
       <c r="B108" s="4"/>
@@ -2576,10 +2328,10 @@
       <c r="G108" s="5"/>
       <c r="H108" s="5"/>
       <c r="I108" s="4"/>
-      <c r="J108" s="18"/>
-      <c r="K108" s="18"/>
-      <c r="L108" s="18"/>
-      <c r="M108" s="18"/>
+      <c r="J108" s="14"/>
+      <c r="K108" s="14"/>
+      <c r="L108" s="14"/>
+      <c r="M108" s="14"/>
     </row>
     <row r="109" spans="2:13">
       <c r="B109" s="4"/>
@@ -2590,10 +2342,10 @@
       <c r="G109" s="5"/>
       <c r="H109" s="5"/>
       <c r="I109" s="4"/>
-      <c r="J109" s="18"/>
-      <c r="K109" s="18"/>
-      <c r="L109" s="18"/>
-      <c r="M109" s="18"/>
+      <c r="J109" s="14"/>
+      <c r="K109" s="14"/>
+      <c r="L109" s="14"/>
+      <c r="M109" s="14"/>
     </row>
     <row r="110" spans="2:13">
       <c r="B110" s="4"/>
@@ -2604,10 +2356,10 @@
       <c r="G110" s="5"/>
       <c r="H110" s="5"/>
       <c r="I110" s="4"/>
-      <c r="J110" s="18"/>
-      <c r="K110" s="18"/>
-      <c r="L110" s="18"/>
-      <c r="M110" s="18"/>
+      <c r="J110" s="14"/>
+      <c r="K110" s="14"/>
+      <c r="L110" s="14"/>
+      <c r="M110" s="14"/>
     </row>
     <row r="111" spans="2:13">
       <c r="B111" s="4"/>
@@ -2618,10 +2370,10 @@
       <c r="G111" s="5"/>
       <c r="H111" s="5"/>
       <c r="I111" s="4"/>
-      <c r="J111" s="18"/>
-      <c r="K111" s="18"/>
-      <c r="L111" s="18"/>
-      <c r="M111" s="18"/>
+      <c r="J111" s="14"/>
+      <c r="K111" s="14"/>
+      <c r="L111" s="14"/>
+      <c r="M111" s="14"/>
     </row>
     <row r="112" spans="2:13">
       <c r="B112" s="4"/>
@@ -2632,10 +2384,10 @@
       <c r="G112" s="5"/>
       <c r="H112" s="5"/>
       <c r="I112" s="4"/>
-      <c r="J112" s="37"/>
-      <c r="K112" s="37"/>
-      <c r="L112" s="37"/>
-      <c r="M112" s="37"/>
+      <c r="J112" s="16"/>
+      <c r="K112" s="16"/>
+      <c r="L112" s="16"/>
+      <c r="M112" s="16"/>
     </row>
     <row r="113" spans="2:13" ht="14.25" customHeight="1">
       <c r="B113" s="6"/>
@@ -2687,10 +2439,10 @@
       <c r="G116" s="5"/>
       <c r="H116" s="5"/>
       <c r="I116" s="4"/>
-      <c r="J116" s="15"/>
-      <c r="K116" s="15"/>
-      <c r="L116" s="15"/>
-      <c r="M116" s="15"/>
+      <c r="J116" s="17"/>
+      <c r="K116" s="17"/>
+      <c r="L116" s="17"/>
+      <c r="M116" s="17"/>
     </row>
     <row r="117" spans="2:13" ht="15">
       <c r="B117" s="4"/>
@@ -2701,10 +2453,10 @@
       <c r="G117" s="5"/>
       <c r="H117" s="5"/>
       <c r="I117" s="4"/>
-      <c r="J117" s="17"/>
-      <c r="K117" s="17"/>
-      <c r="L117" s="17"/>
-      <c r="M117" s="17"/>
+      <c r="J117" s="18"/>
+      <c r="K117" s="18"/>
+      <c r="L117" s="18"/>
+      <c r="M117" s="18"/>
     </row>
     <row r="118" spans="2:13">
       <c r="B118" s="4"/>
@@ -2715,10 +2467,10 @@
       <c r="G118" s="5"/>
       <c r="H118" s="5"/>
       <c r="I118" s="4"/>
-      <c r="J118" s="18"/>
-      <c r="K118" s="18"/>
-      <c r="L118" s="18"/>
-      <c r="M118" s="18"/>
+      <c r="J118" s="14"/>
+      <c r="K118" s="14"/>
+      <c r="L118" s="14"/>
+      <c r="M118" s="14"/>
     </row>
     <row r="119" spans="2:13">
       <c r="B119" s="4"/>
@@ -2729,10 +2481,10 @@
       <c r="G119" s="5"/>
       <c r="H119" s="5"/>
       <c r="I119" s="4"/>
-      <c r="J119" s="18"/>
-      <c r="K119" s="18"/>
-      <c r="L119" s="18"/>
-      <c r="M119" s="18"/>
+      <c r="J119" s="14"/>
+      <c r="K119" s="14"/>
+      <c r="L119" s="14"/>
+      <c r="M119" s="14"/>
     </row>
     <row r="120" spans="2:13">
       <c r="B120" s="4"/>
@@ -2743,10 +2495,10 @@
       <c r="G120" s="5"/>
       <c r="H120" s="5"/>
       <c r="I120" s="4"/>
-      <c r="J120" s="28"/>
-      <c r="K120" s="28"/>
-      <c r="L120" s="28"/>
-      <c r="M120" s="28"/>
+      <c r="J120" s="15"/>
+      <c r="K120" s="15"/>
+      <c r="L120" s="15"/>
+      <c r="M120" s="15"/>
     </row>
     <row r="121" spans="2:13">
       <c r="B121" s="4"/>
@@ -2757,10 +2509,10 @@
       <c r="G121" s="5"/>
       <c r="H121" s="5"/>
       <c r="I121" s="4"/>
-      <c r="J121" s="28"/>
-      <c r="K121" s="28"/>
-      <c r="L121" s="28"/>
-      <c r="M121" s="28"/>
+      <c r="J121" s="15"/>
+      <c r="K121" s="15"/>
+      <c r="L121" s="15"/>
+      <c r="M121" s="15"/>
     </row>
     <row r="122" spans="2:13">
       <c r="B122" s="4"/>
@@ -2771,10 +2523,10 @@
       <c r="G122" s="5"/>
       <c r="H122" s="5"/>
       <c r="I122" s="4"/>
-      <c r="J122" s="18"/>
-      <c r="K122" s="18"/>
-      <c r="L122" s="18"/>
-      <c r="M122" s="18"/>
+      <c r="J122" s="14"/>
+      <c r="K122" s="14"/>
+      <c r="L122" s="14"/>
+      <c r="M122" s="14"/>
     </row>
     <row r="123" spans="2:13">
       <c r="B123" s="4"/>
@@ -2785,10 +2537,10 @@
       <c r="G123" s="5"/>
       <c r="H123" s="5"/>
       <c r="I123" s="4"/>
-      <c r="J123" s="18"/>
-      <c r="K123" s="18"/>
-      <c r="L123" s="18"/>
-      <c r="M123" s="18"/>
+      <c r="J123" s="14"/>
+      <c r="K123" s="14"/>
+      <c r="L123" s="14"/>
+      <c r="M123" s="14"/>
     </row>
     <row r="124" spans="2:13">
       <c r="B124" s="4"/>
@@ -2799,10 +2551,10 @@
       <c r="G124" s="5"/>
       <c r="H124" s="5"/>
       <c r="I124" s="4"/>
-      <c r="J124" s="18"/>
-      <c r="K124" s="18"/>
-      <c r="L124" s="18"/>
-      <c r="M124" s="18"/>
+      <c r="J124" s="14"/>
+      <c r="K124" s="14"/>
+      <c r="L124" s="14"/>
+      <c r="M124" s="14"/>
     </row>
     <row r="125" spans="2:13">
       <c r="B125" s="4"/>
@@ -2813,10 +2565,10 @@
       <c r="G125" s="5"/>
       <c r="H125" s="5"/>
       <c r="I125" s="4"/>
-      <c r="J125" s="18"/>
-      <c r="K125" s="18"/>
-      <c r="L125" s="18"/>
-      <c r="M125" s="18"/>
+      <c r="J125" s="14"/>
+      <c r="K125" s="14"/>
+      <c r="L125" s="14"/>
+      <c r="M125" s="14"/>
     </row>
     <row r="126" spans="2:13">
       <c r="B126" s="4"/>
@@ -2827,10 +2579,10 @@
       <c r="G126" s="5"/>
       <c r="H126" s="5"/>
       <c r="I126" s="4"/>
-      <c r="J126" s="18"/>
-      <c r="K126" s="18"/>
-      <c r="L126" s="18"/>
-      <c r="M126" s="18"/>
+      <c r="J126" s="14"/>
+      <c r="K126" s="14"/>
+      <c r="L126" s="14"/>
+      <c r="M126" s="14"/>
     </row>
     <row r="127" spans="2:13">
       <c r="B127" s="4"/>
@@ -2841,10 +2593,10 @@
       <c r="G127" s="5"/>
       <c r="H127" s="5"/>
       <c r="I127" s="4"/>
-      <c r="J127" s="18"/>
-      <c r="K127" s="18"/>
-      <c r="L127" s="18"/>
-      <c r="M127" s="18"/>
+      <c r="J127" s="14"/>
+      <c r="K127" s="14"/>
+      <c r="L127" s="14"/>
+      <c r="M127" s="14"/>
     </row>
     <row r="128" spans="2:13">
       <c r="B128" s="4"/>
@@ -2855,10 +2607,10 @@
       <c r="G128" s="5"/>
       <c r="H128" s="5"/>
       <c r="I128" s="4"/>
-      <c r="J128" s="18"/>
-      <c r="K128" s="18"/>
-      <c r="L128" s="18"/>
-      <c r="M128" s="18"/>
+      <c r="J128" s="14"/>
+      <c r="K128" s="14"/>
+      <c r="L128" s="14"/>
+      <c r="M128" s="14"/>
     </row>
     <row r="129" spans="2:13">
       <c r="B129" s="4"/>
@@ -2869,10 +2621,10 @@
       <c r="G129" s="5"/>
       <c r="H129" s="5"/>
       <c r="I129" s="4"/>
-      <c r="J129" s="18"/>
-      <c r="K129" s="18"/>
-      <c r="L129" s="18"/>
-      <c r="M129" s="18"/>
+      <c r="J129" s="14"/>
+      <c r="K129" s="14"/>
+      <c r="L129" s="14"/>
+      <c r="M129" s="14"/>
     </row>
     <row r="130" spans="2:13">
       <c r="B130" s="4"/>
@@ -2883,10 +2635,10 @@
       <c r="G130" s="5"/>
       <c r="H130" s="5"/>
       <c r="I130" s="4"/>
-      <c r="J130" s="18"/>
-      <c r="K130" s="18"/>
-      <c r="L130" s="18"/>
-      <c r="M130" s="18"/>
+      <c r="J130" s="14"/>
+      <c r="K130" s="14"/>
+      <c r="L130" s="14"/>
+      <c r="M130" s="14"/>
     </row>
     <row r="131" spans="2:13">
       <c r="B131" s="4"/>
@@ -2897,10 +2649,10 @@
       <c r="G131" s="5"/>
       <c r="H131" s="5"/>
       <c r="I131" s="4"/>
-      <c r="J131" s="18"/>
-      <c r="K131" s="18"/>
-      <c r="L131" s="18"/>
-      <c r="M131" s="18"/>
+      <c r="J131" s="14"/>
+      <c r="K131" s="14"/>
+      <c r="L131" s="14"/>
+      <c r="M131" s="14"/>
     </row>
     <row r="132" spans="2:13">
       <c r="B132" s="4"/>
@@ -2911,10 +2663,10 @@
       <c r="G132" s="5"/>
       <c r="H132" s="5"/>
       <c r="I132" s="4"/>
-      <c r="J132" s="18"/>
-      <c r="K132" s="18"/>
-      <c r="L132" s="18"/>
-      <c r="M132" s="18"/>
+      <c r="J132" s="14"/>
+      <c r="K132" s="14"/>
+      <c r="L132" s="14"/>
+      <c r="M132" s="14"/>
     </row>
     <row r="133" spans="2:13">
       <c r="B133" s="4"/>
@@ -2925,10 +2677,10 @@
       <c r="G133" s="5"/>
       <c r="H133" s="5"/>
       <c r="I133" s="4"/>
-      <c r="J133" s="18"/>
-      <c r="K133" s="18"/>
-      <c r="L133" s="18"/>
-      <c r="M133" s="18"/>
+      <c r="J133" s="14"/>
+      <c r="K133" s="14"/>
+      <c r="L133" s="14"/>
+      <c r="M133" s="14"/>
     </row>
     <row r="134" spans="2:13">
       <c r="B134" s="4"/>
@@ -2939,10 +2691,10 @@
       <c r="G134" s="5"/>
       <c r="H134" s="5"/>
       <c r="I134" s="4"/>
-      <c r="J134" s="18"/>
-      <c r="K134" s="18"/>
-      <c r="L134" s="18"/>
-      <c r="M134" s="18"/>
+      <c r="J134" s="14"/>
+      <c r="K134" s="14"/>
+      <c r="L134" s="14"/>
+      <c r="M134" s="14"/>
     </row>
     <row r="135" spans="2:13">
       <c r="B135" s="4"/>
@@ -2953,10 +2705,10 @@
       <c r="G135" s="5"/>
       <c r="H135" s="5"/>
       <c r="I135" s="4"/>
-      <c r="J135" s="18"/>
-      <c r="K135" s="18"/>
-      <c r="L135" s="18"/>
-      <c r="M135" s="18"/>
+      <c r="J135" s="14"/>
+      <c r="K135" s="14"/>
+      <c r="L135" s="14"/>
+      <c r="M135" s="14"/>
     </row>
     <row r="136" spans="2:13" ht="14.25" customHeight="1">
       <c r="B136" s="6"/>
@@ -3064,6 +2816,114 @@
     <row r="1360" ht="14.25" customHeight="1"/>
   </sheetData>
   <mergeCells count="123">
+    <mergeCell ref="J1:M1"/>
+    <mergeCell ref="J2:M2"/>
+    <mergeCell ref="J3:M3"/>
+    <mergeCell ref="J4:M4"/>
+    <mergeCell ref="J5:M5"/>
+    <mergeCell ref="J6:M6"/>
+    <mergeCell ref="J7:M7"/>
+    <mergeCell ref="J8:M8"/>
+    <mergeCell ref="J9:M9"/>
+    <mergeCell ref="J10:M10"/>
+    <mergeCell ref="J11:M11"/>
+    <mergeCell ref="J12:M12"/>
+    <mergeCell ref="J13:M13"/>
+    <mergeCell ref="J14:M14"/>
+    <mergeCell ref="J15:M15"/>
+    <mergeCell ref="J16:M16"/>
+    <mergeCell ref="J17:M17"/>
+    <mergeCell ref="J18:M18"/>
+    <mergeCell ref="J19:M19"/>
+    <mergeCell ref="J20:M20"/>
+    <mergeCell ref="J21:M21"/>
+    <mergeCell ref="J24:M24"/>
+    <mergeCell ref="J25:M25"/>
+    <mergeCell ref="J26:M26"/>
+    <mergeCell ref="J27:M27"/>
+    <mergeCell ref="J28:M28"/>
+    <mergeCell ref="J29:M29"/>
+    <mergeCell ref="J30:M30"/>
+    <mergeCell ref="J31:M31"/>
+    <mergeCell ref="J32:M32"/>
+    <mergeCell ref="J33:M33"/>
+    <mergeCell ref="J34:M34"/>
+    <mergeCell ref="J35:M35"/>
+    <mergeCell ref="J36:M36"/>
+    <mergeCell ref="J37:M37"/>
+    <mergeCell ref="J38:M38"/>
+    <mergeCell ref="J39:M39"/>
+    <mergeCell ref="J40:M40"/>
+    <mergeCell ref="J41:M41"/>
+    <mergeCell ref="J42:M42"/>
+    <mergeCell ref="J43:M43"/>
+    <mergeCell ref="J44:M44"/>
+    <mergeCell ref="J47:M47"/>
+    <mergeCell ref="J48:M48"/>
+    <mergeCell ref="J49:M49"/>
+    <mergeCell ref="J50:M50"/>
+    <mergeCell ref="J51:M51"/>
+    <mergeCell ref="J52:M52"/>
+    <mergeCell ref="J53:M53"/>
+    <mergeCell ref="J54:M54"/>
+    <mergeCell ref="J55:M55"/>
+    <mergeCell ref="J56:M56"/>
+    <mergeCell ref="J57:M57"/>
+    <mergeCell ref="J58:M58"/>
+    <mergeCell ref="J59:M59"/>
+    <mergeCell ref="J60:M60"/>
+    <mergeCell ref="J61:M61"/>
+    <mergeCell ref="J62:M62"/>
+    <mergeCell ref="J63:M63"/>
+    <mergeCell ref="J64:M64"/>
+    <mergeCell ref="J65:M65"/>
+    <mergeCell ref="J66:M66"/>
+    <mergeCell ref="J67:M67"/>
+    <mergeCell ref="J70:M70"/>
+    <mergeCell ref="J71:M71"/>
+    <mergeCell ref="J72:M72"/>
+    <mergeCell ref="J73:M73"/>
+    <mergeCell ref="J74:M74"/>
+    <mergeCell ref="J75:M75"/>
+    <mergeCell ref="J76:M76"/>
+    <mergeCell ref="J77:M77"/>
+    <mergeCell ref="J78:M78"/>
+    <mergeCell ref="J79:M79"/>
+    <mergeCell ref="J80:M80"/>
+    <mergeCell ref="J81:M81"/>
+    <mergeCell ref="J82:M82"/>
+    <mergeCell ref="J83:M83"/>
+    <mergeCell ref="J84:M84"/>
+    <mergeCell ref="J85:M85"/>
+    <mergeCell ref="J86:M86"/>
+    <mergeCell ref="J87:M87"/>
+    <mergeCell ref="J88:M88"/>
+    <mergeCell ref="J89:M89"/>
+    <mergeCell ref="J93:M93"/>
+    <mergeCell ref="J94:M94"/>
+    <mergeCell ref="J95:M95"/>
+    <mergeCell ref="J96:M96"/>
+    <mergeCell ref="J97:M97"/>
+    <mergeCell ref="J98:M98"/>
+    <mergeCell ref="J99:M99"/>
+    <mergeCell ref="J100:M100"/>
+    <mergeCell ref="J101:M101"/>
+    <mergeCell ref="J102:M102"/>
+    <mergeCell ref="J103:M103"/>
+    <mergeCell ref="J104:M104"/>
+    <mergeCell ref="J105:M105"/>
+    <mergeCell ref="J106:M106"/>
+    <mergeCell ref="J107:M107"/>
+    <mergeCell ref="J108:M108"/>
+    <mergeCell ref="J109:M109"/>
+    <mergeCell ref="J110:M110"/>
+    <mergeCell ref="J111:M111"/>
+    <mergeCell ref="J112:M112"/>
+    <mergeCell ref="J116:M116"/>
+    <mergeCell ref="J117:M117"/>
+    <mergeCell ref="J118:M118"/>
+    <mergeCell ref="J119:M119"/>
+    <mergeCell ref="J120:M120"/>
     <mergeCell ref="J130:M130"/>
     <mergeCell ref="J131:M131"/>
     <mergeCell ref="J132:M132"/>
@@ -3079,114 +2939,6 @@
     <mergeCell ref="J127:M127"/>
     <mergeCell ref="J128:M128"/>
     <mergeCell ref="J129:M129"/>
-    <mergeCell ref="J109:M109"/>
-    <mergeCell ref="J110:M110"/>
-    <mergeCell ref="J111:M111"/>
-    <mergeCell ref="J112:M112"/>
-    <mergeCell ref="J116:M116"/>
-    <mergeCell ref="J117:M117"/>
-    <mergeCell ref="J118:M118"/>
-    <mergeCell ref="J119:M119"/>
-    <mergeCell ref="J120:M120"/>
-    <mergeCell ref="J100:M100"/>
-    <mergeCell ref="J101:M101"/>
-    <mergeCell ref="J102:M102"/>
-    <mergeCell ref="J103:M103"/>
-    <mergeCell ref="J104:M104"/>
-    <mergeCell ref="J105:M105"/>
-    <mergeCell ref="J106:M106"/>
-    <mergeCell ref="J107:M107"/>
-    <mergeCell ref="J108:M108"/>
-    <mergeCell ref="J88:M88"/>
-    <mergeCell ref="J89:M89"/>
-    <mergeCell ref="J93:M93"/>
-    <mergeCell ref="J94:M94"/>
-    <mergeCell ref="J95:M95"/>
-    <mergeCell ref="J96:M96"/>
-    <mergeCell ref="J97:M97"/>
-    <mergeCell ref="J98:M98"/>
-    <mergeCell ref="J99:M99"/>
-    <mergeCell ref="J79:M79"/>
-    <mergeCell ref="J80:M80"/>
-    <mergeCell ref="J81:M81"/>
-    <mergeCell ref="J82:M82"/>
-    <mergeCell ref="J83:M83"/>
-    <mergeCell ref="J84:M84"/>
-    <mergeCell ref="J85:M85"/>
-    <mergeCell ref="J86:M86"/>
-    <mergeCell ref="J87:M87"/>
-    <mergeCell ref="J70:M70"/>
-    <mergeCell ref="J71:M71"/>
-    <mergeCell ref="J72:M72"/>
-    <mergeCell ref="J73:M73"/>
-    <mergeCell ref="J74:M74"/>
-    <mergeCell ref="J75:M75"/>
-    <mergeCell ref="J76:M76"/>
-    <mergeCell ref="J77:M77"/>
-    <mergeCell ref="J78:M78"/>
-    <mergeCell ref="J59:M59"/>
-    <mergeCell ref="J60:M60"/>
-    <mergeCell ref="J61:M61"/>
-    <mergeCell ref="J62:M62"/>
-    <mergeCell ref="J63:M63"/>
-    <mergeCell ref="J64:M64"/>
-    <mergeCell ref="J65:M65"/>
-    <mergeCell ref="J66:M66"/>
-    <mergeCell ref="J67:M67"/>
-    <mergeCell ref="J50:M50"/>
-    <mergeCell ref="J51:M51"/>
-    <mergeCell ref="J52:M52"/>
-    <mergeCell ref="J53:M53"/>
-    <mergeCell ref="J54:M54"/>
-    <mergeCell ref="J55:M55"/>
-    <mergeCell ref="J56:M56"/>
-    <mergeCell ref="J57:M57"/>
-    <mergeCell ref="J58:M58"/>
-    <mergeCell ref="J39:M39"/>
-    <mergeCell ref="J40:M40"/>
-    <mergeCell ref="J41:M41"/>
-    <mergeCell ref="J42:M42"/>
-    <mergeCell ref="J43:M43"/>
-    <mergeCell ref="J44:M44"/>
-    <mergeCell ref="J47:M47"/>
-    <mergeCell ref="J48:M48"/>
-    <mergeCell ref="J49:M49"/>
-    <mergeCell ref="J30:M30"/>
-    <mergeCell ref="J31:M31"/>
-    <mergeCell ref="J32:M32"/>
-    <mergeCell ref="J33:M33"/>
-    <mergeCell ref="J34:M34"/>
-    <mergeCell ref="J35:M35"/>
-    <mergeCell ref="J36:M36"/>
-    <mergeCell ref="J37:M37"/>
-    <mergeCell ref="J38:M38"/>
-    <mergeCell ref="J19:M19"/>
-    <mergeCell ref="J20:M20"/>
-    <mergeCell ref="J21:M21"/>
-    <mergeCell ref="J24:M24"/>
-    <mergeCell ref="J25:M25"/>
-    <mergeCell ref="J26:M26"/>
-    <mergeCell ref="J27:M27"/>
-    <mergeCell ref="J28:M28"/>
-    <mergeCell ref="J29:M29"/>
-    <mergeCell ref="J10:M10"/>
-    <mergeCell ref="J11:M11"/>
-    <mergeCell ref="J12:M12"/>
-    <mergeCell ref="J13:M13"/>
-    <mergeCell ref="J14:M14"/>
-    <mergeCell ref="J15:M15"/>
-    <mergeCell ref="J16:M16"/>
-    <mergeCell ref="J17:M17"/>
-    <mergeCell ref="J18:M18"/>
-    <mergeCell ref="J1:M1"/>
-    <mergeCell ref="J2:M2"/>
-    <mergeCell ref="J3:M3"/>
-    <mergeCell ref="J4:M4"/>
-    <mergeCell ref="J5:M5"/>
-    <mergeCell ref="J6:M6"/>
-    <mergeCell ref="J7:M7"/>
-    <mergeCell ref="J8:M8"/>
-    <mergeCell ref="J9:M9"/>
   </mergeCells>
   <phoneticPr fontId="16"/>
   <pageMargins left="0.78749999999999998" right="0" top="0.39374999999999999" bottom="0" header="0.511811023622047" footer="0.511811023622047"/>
